--- a/data/trans_dic/P1403-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1403-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 17,46</t>
+          <t>9,68; 17,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,2</t>
+          <t>7,95; 15,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 16,03</t>
+          <t>8,08; 16,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 24,55</t>
+          <t>17,05; 25,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 19,49</t>
+          <t>10,42; 19,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 19,43</t>
+          <t>11,1; 20,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,03</t>
+          <t>8,19; 15,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 23,61</t>
+          <t>15,37; 21,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 17,0</t>
+          <t>11,19; 16,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,03</t>
+          <t>10,48; 16,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 15,11</t>
+          <t>9,29; 14,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 22,75</t>
+          <t>17,54; 23,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,69</t>
+          <t>6,99; 12,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,99</t>
+          <t>12,83; 20,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 20,35</t>
+          <t>13,45; 20,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,09; 20,17</t>
+          <t>13,46; 20,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 21,12</t>
+          <t>14,52; 20,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 24,23</t>
+          <t>16,55; 23,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,89; 26,58</t>
+          <t>18,92; 26,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,64; 18,59</t>
+          <t>13,57; 18,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,04</t>
+          <t>11,46; 15,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 20,82</t>
+          <t>15,72; 20,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 22,33</t>
+          <t>17,39; 22,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,01; 18,27</t>
+          <t>14,08; 18,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 18,63</t>
+          <t>10,72; 18,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,24</t>
+          <t>14,57; 23,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 18,59</t>
+          <t>11,16; 19,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 24,59</t>
+          <t>16,63; 23,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 25,61</t>
+          <t>16,89; 25,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 27,61</t>
+          <t>18,54; 27,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,66</t>
+          <t>11,73; 19,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 26,01</t>
+          <t>18,44; 25,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,21; 20,86</t>
+          <t>15,02; 20,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 24,16</t>
+          <t>17,85; 24,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 17,91</t>
+          <t>12,44; 17,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 24,01</t>
+          <t>18,62; 23,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,27; 18,28</t>
+          <t>11,31; 18,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 22,82</t>
+          <t>14,1; 22,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 21,2</t>
+          <t>13,11; 21,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 26,04</t>
+          <t>15,24; 23,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 22,7</t>
+          <t>14,89; 22,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 30,11</t>
+          <t>20,95; 30,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,94; 24,69</t>
+          <t>15,88; 24,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,53; 24,0</t>
+          <t>19,28; 25,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 18,99</t>
+          <t>14,08; 19,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 25,22</t>
+          <t>19,04; 25,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 21,44</t>
+          <t>15,71; 21,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,12; 22,82</t>
+          <t>18,38; 23,54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,28</t>
+          <t>4,68; 12,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 20,97</t>
+          <t>10,66; 20,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,9</t>
+          <t>8,33; 18,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,64; 29,96</t>
+          <t>18,06; 27,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,34</t>
+          <t>10,28; 20,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,69; 32,81</t>
+          <t>21,08; 32,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,17; 25,32</t>
+          <t>14,67; 26,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,3; 33,76</t>
+          <t>24,09; 31,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 14,51</t>
+          <t>8,23; 14,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,3</t>
+          <t>16,68; 24,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 20,24</t>
+          <t>12,81; 19,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,87; 30,49</t>
+          <t>22,1; 28,13</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,34; 19,55</t>
+          <t>11,19; 20,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 28,68</t>
+          <t>18,09; 28,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,01; 18,09</t>
+          <t>10,14; 18,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,96; 31,76</t>
+          <t>22,55; 31,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,54; 23,65</t>
+          <t>14,47; 24,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,36; 28,64</t>
+          <t>17,79; 27,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,44; 22,84</t>
+          <t>12,9; 22,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 27,63</t>
+          <t>20,26; 27,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 20,24</t>
+          <t>13,8; 20,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 26,62</t>
+          <t>19,16; 26,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,47; 18,6</t>
+          <t>12,58; 19,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,9; 28,65</t>
+          <t>22,59; 28,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 17,63</t>
+          <t>11,91; 17,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,97; 22,43</t>
+          <t>15,88; 22,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 17,28</t>
+          <t>11,79; 17,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,58</t>
+          <t>15,16; 21,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,43; 20,54</t>
+          <t>14,3; 20,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,11; 26,37</t>
+          <t>19,69; 26,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,34</t>
+          <t>11,35; 17,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,9; 69,49</t>
+          <t>18,69; 23,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,74; 17,76</t>
+          <t>13,79; 17,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,94; 23,4</t>
+          <t>18,75; 23,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,45; 16,43</t>
+          <t>12,5; 16,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,62; 58,03</t>
+          <t>18,01; 21,94</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,34; 16,0</t>
+          <t>11,32; 15,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,57</t>
+          <t>11,88; 17,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,15; 19,34</t>
+          <t>14,05; 19,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 18,28</t>
+          <t>14,38; 19,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 16,81</t>
+          <t>11,84; 17,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 19,87</t>
+          <t>14,42; 19,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,43; 22,41</t>
+          <t>16,34; 22,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,36; 24,71</t>
+          <t>18,56; 23,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,8</t>
+          <t>12,19; 15,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,83; 17,82</t>
+          <t>14,02; 17,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,03</t>
+          <t>16,01; 20,05</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,21; 20,44</t>
+          <t>17,21; 20,62</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,96; 14,33</t>
+          <t>11,93; 14,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,06</t>
+          <t>15,5; 18,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,95; 16,36</t>
+          <t>13,84; 16,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,0; 19,94</t>
+          <t>17,94; 20,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,77; 18,24</t>
+          <t>15,79; 18,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,29</t>
+          <t>19,56; 22,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,45; 19,08</t>
+          <t>16,45; 19,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,3; 40,41</t>
+          <t>19,86; 22,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,25; 15,91</t>
+          <t>14,04; 15,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,81</t>
+          <t>17,99; 19,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,52; 17,32</t>
+          <t>15,61; 17,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,79; 29,88</t>
+          <t>19,27; 20,9</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>68949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57790</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>119542</t>
+          <t>128271</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26657; 47678</t>
+          <t>26435; 48536</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22588; 44811</t>
+          <t>23419; 45983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24266; 47098</t>
+          <t>23750; 48339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49142; 76462</t>
+          <t>54364; 82657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27978; 50828</t>
+          <t>27182; 50077</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31507; 55814</t>
+          <t>31872; 58250</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24114; 46288</t>
+          <t>23646; 46091</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48625; 68396</t>
+          <t>48574; 69451</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60296; 90735</t>
+          <t>59737; 89721</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61148; 93285</t>
+          <t>61006; 94305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53182; 88001</t>
+          <t>54138; 85661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>103679; 136717</t>
+          <t>111341; 146650</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84880</t>
+          <t>87740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81672</t>
+          <t>86948</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>166552</t>
+          <t>174687</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35799; 62553</t>
+          <t>34462; 61057</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66338; 101065</t>
+          <t>64848; 101506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67559; 102282</t>
+          <t>67590; 101597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67716; 104338</t>
+          <t>71270; 108543</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72432; 106454</t>
+          <t>73169; 105341</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87378; 126648</t>
+          <t>86493; 124372</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98818; 139020</t>
+          <t>98949; 138689</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69904; 95289</t>
+          <t>73834; 101117</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>113979; 159875</t>
+          <t>114309; 158563</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161738; 214089</t>
+          <t>161638; 213118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177100; 228991</t>
+          <t>178384; 230101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>144302; 188128</t>
+          <t>151127; 197517</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63673</t>
+          <t>62993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76921</t>
+          <t>78055</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>140593</t>
+          <t>141048</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35430; 59389</t>
+          <t>34189; 59662</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46355; 75307</t>
+          <t>47217; 74680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35267; 59208</t>
+          <t>35558; 60712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52045; 77329</t>
+          <t>52292; 75138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56561; 85896</t>
+          <t>56645; 86116</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64247; 94171</t>
+          <t>63231; 95304</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38626; 66118</t>
+          <t>39437; 67121</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65968; 90793</t>
+          <t>65716; 89642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99487; 136479</t>
+          <t>98286; 137301</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117988; 160694</t>
+          <t>118719; 162717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80708; 117275</t>
+          <t>81476; 117177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>123878; 159317</t>
+          <t>124935; 158225</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>71812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>87279</t>
+          <t>94217</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>151986</t>
+          <t>166029</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40413; 65581</t>
+          <t>40554; 65743</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53210; 85340</t>
+          <t>52722; 84270</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49359; 78415</t>
+          <t>48492; 78130</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51304; 81404</t>
+          <t>56851; 88807</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54668; 84314</t>
+          <t>55325; 83985</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83148; 117101</t>
+          <t>81471; 116933</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61727; 95616</t>
+          <t>61500; 95993</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54867; 114159</t>
+          <t>81367; 107096</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102247; 138637</t>
+          <t>102805; 140645</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>144938; 192394</t>
+          <t>145227; 190988</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117765; 162342</t>
+          <t>118977; 164398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>111342; 179900</t>
+          <t>146118; 187162</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>46457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>62807</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>104446</t>
+          <t>109264</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9829; 24967</t>
+          <t>9520; 24889</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21433; 44586</t>
+          <t>22663; 43635</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18308; 37807</t>
+          <t>17601; 38605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35103; 53546</t>
+          <t>37146; 56663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20703; 42247</t>
+          <t>21354; 42650</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45442; 72038</t>
+          <t>46290; 70917</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33153; 55347</t>
+          <t>32067; 57220</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52601; 70179</t>
+          <t>54557; 71956</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34851; 59651</t>
+          <t>33805; 59833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72376; 109353</t>
+          <t>72081; 107017</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57170; 87000</t>
+          <t>55046; 85411</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92297; 117872</t>
+          <t>95509; 121566</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73066</t>
+          <t>72071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>62501</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>133536</t>
+          <t>134572</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30708; 52935</t>
+          <t>30313; 54416</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48626; 78566</t>
+          <t>49570; 79291</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26349; 47605</t>
+          <t>26669; 47955</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61912; 85638</t>
+          <t>61052; 84892</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>40443; 65777</t>
+          <t>40249; 67029</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51064; 79649</t>
+          <t>49466; 77798</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36720; 62384</t>
+          <t>35231; 61416</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52113; 70842</t>
+          <t>53306; 72529</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>76928; 111107</t>
+          <t>75778; 111330</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108414; 146964</t>
+          <t>105765; 146613</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66880; 99741</t>
+          <t>67457; 102733</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>120434; 150683</t>
+          <t>120563; 151043</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109869</t>
+          <t>131258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>338078</t>
+          <t>164100</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>447947</t>
+          <t>295358</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73028; 108448</t>
+          <t>73251; 108594</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105846; 148665</t>
+          <t>105264; 150158</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76334; 113429</t>
+          <t>77416; 113808</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90635; 128155</t>
+          <t>108618; 152491</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92119; 131120</t>
+          <t>91297; 130491</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>139548; 182955</t>
+          <t>136585; 183660</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80143; 119836</t>
+          <t>78431; 117842</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>168866; 589596</t>
+          <t>144062; 184191</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>172214; 222523</t>
+          <t>172836; 222144</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>256998; 317502</t>
+          <t>254384; 314729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167801; 221399</t>
+          <t>168514; 221056</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>273900; 853685</t>
+          <t>267812; 326238</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120080</t>
+          <t>133990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>156549</t>
+          <t>173158</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>276629</t>
+          <t>307148</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>84341; 119043</t>
+          <t>84201; 118549</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>95264; 136923</t>
+          <t>92528; 133802</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>110155; 150560</t>
+          <t>109375; 154294</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54933; 169804</t>
+          <t>114748; 153800</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>90553; 131702</t>
+          <t>92762; 133348</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>115080; 163411</t>
+          <t>118646; 162121</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>135748; 185115</t>
+          <t>134967; 181943</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>138502; 176795</t>
+          <t>154162; 193791</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>184604; 241278</t>
+          <t>186177; 239583</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>221537; 285411</t>
+          <t>224583; 284784</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257943; 321355</t>
+          <t>256896; 321810</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>167879; 336097</t>
+          <t>280342; 335855</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>621253</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>919978</t>
+          <t>781108</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1541231</t>
+          <t>1456378</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>391893; 469366</t>
+          <t>390835; 467759</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>529427; 618780</t>
+          <t>531292; 625083</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473573; 555243</t>
+          <t>469734; 553028</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>483909; 689114</t>
+          <t>632575; 724668</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>533039; 616523</t>
+          <t>533685; 618416</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>691577; 792112</t>
+          <t>695173; 796731</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>582971; 676205</t>
+          <t>583146; 679166</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>742025; 1477015</t>
+          <t>740525; 822721</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>948521; 1059189</t>
+          <t>934256; 1053357</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1257558; 1382834</t>
+          <t>1256085; 1389061</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1077061; 1201718</t>
+          <t>1083303; 1215326</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1335900; 2124866</t>
+          <t>1398603; 1516704</t>
         </is>
       </c>
     </row>
